--- a/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>419 COLIBRI</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-13.52134</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-71.98845</v>
-      </c>
-      <c r="I2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-13.52134</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-71.98845</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>50707 SIMON BOLIVAR</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-13.51909</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-71.99191999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>859</v>
-      </c>
-      <c r="J3" t="n">
-        <v>47</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-13.51909</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-71.99192</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>50003 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-13.52107</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-71.97748</v>
-      </c>
-      <c r="I4" t="n">
-        <v>430</v>
-      </c>
-      <c r="J4" t="n">
-        <v>23</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-13.52107</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-71.97748</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>87</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-13.51749</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-71.98641000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>239</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-13.51749</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-71.98641</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>88</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-13.51926</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-71.97342999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>448</v>
-      </c>
-      <c r="J6" t="n">
-        <v>18</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-13.51926</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-71.97343</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>89</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-13.51986</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-71.9641</v>
-      </c>
-      <c r="I7" t="n">
-        <v>249</v>
-      </c>
-      <c r="J7" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-13.51986</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-71.9641</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>50002 LUIS VALLEJOS SANTONI</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-13.52344</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-71.99102999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1050</v>
-      </c>
-      <c r="J8" t="n">
-        <v>55</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-13.52344</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-71.99103</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>HUMBERTO LUNA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-13.52399</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-71.97655</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1912</v>
-      </c>
-      <c r="J9" t="n">
-        <v>91</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-13.52399</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-71.97655</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-13.52069</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-71.96648</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3870</v>
-      </c>
-      <c r="J10" t="n">
-        <v>149</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-13.52069</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-71.96648</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-13.51993</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-71.96984</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2866</v>
-      </c>
-      <c r="J11" t="n">
-        <v>131</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-13.51993</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-71.96984</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>50022 JORGE CHAVEZ CHAPARRO / JORGE CHAVEZ CHAPARRO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-13.52214</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-71.95226</v>
-      </c>
-      <c r="I12" t="n">
-        <v>704</v>
-      </c>
-      <c r="J12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-13.52214</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-71.95226</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>50023 REPUBLICA DE MEXICO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-13.51796</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-71.96534</v>
-      </c>
-      <c r="I13" t="n">
-        <v>531</v>
-      </c>
-      <c r="J13" t="n">
-        <v>25</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-13.51796</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-71.96534</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>50021</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-13.51314</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-71.97915</v>
-      </c>
-      <c r="I14" t="n">
-        <v>215</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-13.51314</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-71.97915</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>50028</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-13.51909</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-71.95981999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>216</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-13.51909</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-71.95982</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>50048 LOS INCAS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-13.51907</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-71.95269999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>304</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-13.51907</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-71.9527</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>EL NIÑO DIVINO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-13.505664</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-71.99961</v>
-      </c>
-      <c r="I17" t="n">
-        <v>293</v>
-      </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-13.505664</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-71.99961</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>50828 ASHID KUMAR BAHAL</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-13.51896</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-71.98663999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>412</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-13.51896</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-71.98664</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>50900 EDUCANDAS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-13.51689</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-71.9821</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1378</v>
-      </c>
-      <c r="J19" t="n">
-        <v>73</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-13.51689</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-71.9821</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>51002 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-13.51734</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-71.98372000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>594</v>
-      </c>
-      <c r="J20" t="n">
-        <v>33</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-13.51734</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-71.98372</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>51003 ROSARIO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-13.52335</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-71.9773</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1327</v>
-      </c>
-      <c r="J21" t="n">
-        <v>57</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-13.52335</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-71.9773</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>51004 SAN VICENTE DE PAUL</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-13.51869</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-71.98487</v>
-      </c>
-      <c r="I22" t="n">
-        <v>774</v>
-      </c>
-      <c r="J22" t="n">
-        <v>40</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-13.51869</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-71.98487</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-13.52157</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-71.97846</v>
-      </c>
-      <c r="I23" t="n">
-        <v>695</v>
-      </c>
-      <c r="J23" t="n">
-        <v>31</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-13.52157</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-71.97846</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-13.51907</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-71.98193000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2399</v>
-      </c>
-      <c r="J24" t="n">
-        <v>114</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-13.51907</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-71.98193</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2399</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>51009 FRANCISCO SIVIRICHI</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-13.51732</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-71.98267</v>
-      </c>
-      <c r="I25" t="n">
-        <v>707</v>
-      </c>
-      <c r="J25" t="n">
-        <v>32</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-13.51732</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-71.98267</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-13.51552</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-71.98855</v>
-      </c>
-      <c r="I26" t="n">
-        <v>275</v>
-      </c>
-      <c r="J26" t="n">
-        <v>15</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-13.51552</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-71.98855</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>51015 SAN FRANCISCO DE BORJA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-13.51544</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-71.9786</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1515</v>
-      </c>
-      <c r="J27" t="n">
-        <v>71</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-13.51544</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-71.9786</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>51017</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-13.52007</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-71.96245999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>619</v>
-      </c>
-      <c r="J28" t="n">
-        <v>29</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-13.52007</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-71.96246</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>COMERCIO 41</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-13.52018</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-71.96442999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>811</v>
-      </c>
-      <c r="J29" t="n">
-        <v>48</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-13.52018</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-71.96443</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>FORTUNATO L HERRERA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-13.51971</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-71.97136</v>
-      </c>
-      <c r="I30" t="n">
-        <v>544</v>
-      </c>
-      <c r="J30" t="n">
-        <v>106</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-13.51971</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-71.97136</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>SAN ANTONIO ABAD</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-13.5258</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-71.95018</v>
-      </c>
-      <c r="I31" t="n">
-        <v>569</v>
-      </c>
-      <c r="J31" t="n">
-        <v>34</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-13.5258</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-71.95018</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>NUESTRA SEÑORA DE GRACIA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-13.51556</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-71.95138</v>
-      </c>
-      <c r="I32" t="n">
-        <v>242</v>
-      </c>
-      <c r="J32" t="n">
-        <v>13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-13.51556</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-71.95138</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>LA MERCED</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-13.51851</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-71.97872</v>
-      </c>
-      <c r="I33" t="n">
-        <v>938</v>
-      </c>
-      <c r="J33" t="n">
-        <v>47</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-13.51851</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-71.97872</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN JUAN DE DIOS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-13.51719</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-71.98146</v>
-      </c>
-      <c r="I34" t="n">
-        <v>259</v>
-      </c>
-      <c r="J34" t="n">
-        <v>16</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-13.51719</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-71.98146</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>JOSE PARDO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-13.52472</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-71.97429</v>
-      </c>
-      <c r="I35" t="n">
-        <v>502</v>
-      </c>
-      <c r="J35" t="n">
-        <v>30</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-13.52472</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-71.97429</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-13.5145</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-71.97758</v>
-      </c>
-      <c r="I36" t="n">
-        <v>638</v>
-      </c>
-      <c r="J36" t="n">
-        <v>36</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-13.5145</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-71.97758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>EL CARMELO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-13.51544</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-71.97453</v>
-      </c>
-      <c r="I37" t="n">
-        <v>495</v>
-      </c>
-      <c r="J37" t="n">
-        <v>37</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-13.51544</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-71.97453</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SALESIANO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-13.51334</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-71.98098</v>
-      </c>
-      <c r="I38" t="n">
-        <v>918</v>
-      </c>
-      <c r="J38" t="n">
-        <v>51</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-13.51334</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-71.98098</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-13.51825</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-71.9833</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1110</v>
-      </c>
-      <c r="J39" t="n">
-        <v>64</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-13.51825</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-71.9833</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-13.52034</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-71.97633</v>
-      </c>
-      <c r="I40" t="n">
-        <v>444</v>
-      </c>
-      <c r="J40" t="n">
-        <v>26</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-13.52034</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-71.97633</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-13.52171</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-71.97454999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>577</v>
-      </c>
-      <c r="J41" t="n">
-        <v>39</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-13.52171</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-71.97455</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>577</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-13.52103</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-71.97472</v>
-      </c>
-      <c r="I42" t="n">
-        <v>631</v>
-      </c>
-      <c r="J42" t="n">
-        <v>41</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-13.52103</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-71.97472</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>JUAN LANDAZURI RICKETTS</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-13.52612</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-71.94926</v>
-      </c>
-      <c r="I43" t="n">
-        <v>299</v>
-      </c>
-      <c r="J43" t="n">
-        <v>25</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-13.52612</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-71.94926</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>AVANTI PERU</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-13.5201</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-71.98465</v>
-      </c>
-      <c r="I44" t="n">
-        <v>283</v>
-      </c>
-      <c r="J44" t="n">
-        <v>22</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-13.5201</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-71.98465</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>BERNABE COBO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-13.51953</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-71.98321</v>
-      </c>
-      <c r="I45" t="n">
-        <v>483</v>
-      </c>
-      <c r="J45" t="n">
-        <v>29</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-13.51953</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-71.98321</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>PROYECTO INGENIERIA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-13.52502</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-71.97496</v>
-      </c>
-      <c r="I46" t="n">
-        <v>171</v>
-      </c>
-      <c r="J46" t="n">
-        <v>16</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-13.52502</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-71.97496</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>50014 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-13.541976</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-71.948846</v>
-      </c>
-      <c r="I47" t="n">
-        <v>337</v>
-      </c>
-      <c r="J47" t="n">
-        <v>17</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-13.541976</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-71.948846</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>50949 EL CARMELO DE MARIA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-13.507337</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-71.933803</v>
-      </c>
-      <c r="I48" t="n">
-        <v>349</v>
-      </c>
-      <c r="J48" t="n">
-        <v>21</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-13.507337</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-71.933803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>50941</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-13.52747</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-71.99165000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>392</v>
-      </c>
-      <c r="J49" t="n">
-        <v>21</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-13.52747</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-71.99165</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>50036</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-13.56926</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-71.82726</v>
-      </c>
-      <c r="I50" t="n">
-        <v>374</v>
-      </c>
-      <c r="J50" t="n">
-        <v>16</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-13.56926</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-71.82726</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-13.56911</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-71.82768</v>
-      </c>
-      <c r="I51" t="n">
-        <v>332</v>
-      </c>
-      <c r="J51" t="n">
-        <v>21</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-13.56911</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-71.82768</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>NUESTRA SEÑORA VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-13.526182</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-71.945517</v>
-      </c>
-      <c r="I52" t="n">
-        <v>272</v>
-      </c>
-      <c r="J52" t="n">
-        <v>22</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-13.526182</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-71.945517</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>LIDERES</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-13.525718</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-71.945415</v>
-      </c>
-      <c r="I53" t="n">
-        <v>227</v>
-      </c>
-      <c r="J53" t="n">
-        <v>12</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-13.525718</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-71.945415</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>SAN GABRIEL DE LOS CIELOS</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-13.50694</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-71.99924</v>
-      </c>
-      <c r="I54" t="n">
-        <v>36</v>
-      </c>
-      <c r="J54" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-13.50694</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-71.99924</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>984</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-13.50338</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-72.0234</v>
-      </c>
-      <c r="I55" t="n">
-        <v>35</v>
-      </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-13.50338</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-72.0234</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>SOR ANA DE LOS ANGELES MONTEAGUDO</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-13.52493</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-71.9757</v>
-      </c>
-      <c r="I56" t="n">
-        <v>44</v>
-      </c>
-      <c r="J56" t="n">
-        <v>4</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-13.52493</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-71.9757</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-13.52182</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-71.94898999999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>595</v>
-      </c>
-      <c r="J57" t="n">
-        <v>27</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-13.52182</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-71.94899</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>GAL SCHOOL</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-13.52637</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-71.90222</v>
-      </c>
-      <c r="I58" t="n">
-        <v>358</v>
-      </c>
-      <c r="J58" t="n">
-        <v>27</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-13.52637</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-71.90222</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>BILINGÜE MANUEL PARDO Y LAVALLE</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-13.52745</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-71.94383000000001</v>
-      </c>
-      <c r="I59" t="n">
-        <v>267</v>
-      </c>
-      <c r="J59" t="n">
-        <v>16</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-13.52745</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-71.94383</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>SAMI RURUCHA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-13.548</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-71.88039999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>29</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-13.548</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-71.8804</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,27 +501,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>145913</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>419 COLIBRI</t>
+          <t>439 NIÑOS DE AMERICA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.52134</t>
+          <t>-13.51873</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.98845</t>
+          <t>-71.96018</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>146106</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50707 SIMON BOLIVAR</t>
+          <t>204 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.51909</t>
+          <t>-13.52478</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.99192</t>
+          <t>-71.94585</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>131</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>146031</t>
+          <t>862720</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50003 SANTA ROSA</t>
+          <t>KAIZEN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-13.52107</t>
+          <t>-13.52224</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-71.97748</t>
+          <t>-71.94719</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.51926</t>
+          <t>-13.51909</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.97343</t>
+          <t>-71.95982</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>146074</t>
+          <t>146446</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>FORTUNATO L HERRERA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.51986</t>
+          <t>-13.51971</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.9641</t>
+          <t>-71.97136</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>544</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>146130</t>
+          <t>146229</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50002 LUIS VALLEJOS SANTONI</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.52344</t>
+          <t>-13.51314</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.99103</t>
+          <t>-71.97915</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>146154</t>
+          <t>146352</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HUMBERTO LUNA</t>
+          <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.52399</t>
+          <t>-13.51907</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.97655</t>
+          <t>-71.98193</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>146187</t>
+          <t>146074</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INCA GARCILASO DE LA VEGA</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.52069</t>
+          <t>-13.51986</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.96648</t>
+          <t>-71.9641</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>249</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,42 +1059,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>146192</t>
+          <t>146267</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CLORINDA MATTO DE TURNER</t>
+          <t>EL NIÑO DIVINO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.51993</t>
+          <t>-13.505664</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.96984</t>
+          <t>-71.99961</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>146205</t>
+          <t>493097</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50022 JORGE CHAVEZ CHAPARRO / JORGE CHAVEZ CHAPARRO</t>
+          <t>LIDERES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.52214</t>
+          <t>-13.525718</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.95226</t>
+          <t>-71.945415</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>146210</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>50023 REPUBLICA DE MEXICO</t>
+          <t>NUESTRA SEÑORA DE GRACIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.51796</t>
+          <t>-13.51556</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.96534</t>
+          <t>-71.95138</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>146229</t>
+          <t>146192</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.51314</t>
+          <t>-13.51993</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.97915</t>
+          <t>-71.96984</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>146234</t>
+          <t>146187</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.51909</t>
+          <t>-13.52069</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.95982</t>
+          <t>-71.96648</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>146267</t>
+          <t>146371</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EL NIÑO DIVINO</t>
+          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.505664</t>
+          <t>-13.51552</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.99961</t>
+          <t>-71.98855</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>146272</t>
+          <t>146700</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>50828 ASHID KUMAR BAHAL</t>
+          <t>SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.51896</t>
+          <t>-13.51719</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.98664</t>
+          <t>-71.98146</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,42 +1555,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>146286</t>
+          <t>147356</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50900 EDUCANDAS</t>
+          <t>PROYECTO INGENIERIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.51689</t>
+          <t>-13.52502</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.9821</t>
+          <t>-71.97496</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>146314</t>
+          <t>148836</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51002 ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.51734</t>
+          <t>-13.56926</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.98372</t>
+          <t>-71.82726</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>374</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>146328</t>
+          <t>863673</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51003 ROSARIO</t>
+          <t>BILINGÜE MANUEL PARDO Y LAVALLE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.52335</t>
+          <t>-13.52745</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.9773</t>
+          <t>-71.94383</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>147988</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51004 SAN VICENTE DE PAUL</t>
+          <t>50014 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.51869</t>
+          <t>-13.541976</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.98487</t>
+          <t>-71.948846</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>146347</t>
+          <t>146069</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VALENTIN PANIAGUA CORAZAO</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.52157</t>
+          <t>-13.51926</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.97846</t>
+          <t>-71.97343</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>146272</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
+          <t>50828 ASHID KUMAR BAHAL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.51907</t>
+          <t>-13.51896</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.98193</t>
+          <t>-71.98664</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>146366</t>
+          <t>680598</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>51009 FRANCISCO SIVIRICHI</t>
+          <t>984</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.51732</t>
+          <t>-13.50338</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-71.98267</t>
+          <t>-72.0234</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>146371</t>
+          <t>906856</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
+          <t>SAMI RURUCHA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.51552</t>
+          <t>-13.548</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.98855</t>
+          <t>-71.8804</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>148092</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>51015 SAN FRANCISCO DE BORJA</t>
+          <t>50949 EL CARMELO DE MARIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.51544</t>
+          <t>-13.507337</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.9786</t>
+          <t>-71.933803</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>146390</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.52007</t>
+          <t>-13.52747</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.96246</t>
+          <t>-71.99165</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>146432</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COMERCIO 41</t>
+          <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.52018</t>
+          <t>-13.56911</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.96443</t>
+          <t>-71.82768</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>332</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>146446</t>
+          <t>146941</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FORTUNATO L HERRERA</t>
+          <t>AVANTI PERU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.51971</t>
+          <t>-13.5201</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.97136</t>
+          <t>-71.98465</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>146564</t>
+          <t>149379</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAN ANTONIO ABAD</t>
+          <t>NUESTRA SEÑORA VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.5258</t>
+          <t>-13.526182</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.95018</t>
+          <t>-71.945517</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>146578</t>
+          <t>146031</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GRACIA</t>
+          <t>50003 SANTA ROSA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.51556</t>
+          <t>-13.52107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.95138</t>
+          <t>-71.97748</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>146597</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LA MERCED</t>
+          <t>50023 REPUBLICA DE MEXICO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.51851</t>
+          <t>-13.51796</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.97872</t>
+          <t>-71.96534</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>531</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>146700</t>
+          <t>146875</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS</t>
+          <t>JUAN LANDAZURI RICKETTS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.51719</t>
+          <t>-13.52612</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.98146</t>
+          <t>-71.94926</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>146719</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JOSE PARDO</t>
+          <t>LAS MERCEDES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.52472</t>
+          <t>-13.52034</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.97429</t>
+          <t>-71.97633</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>824361</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-13.5145</t>
+          <t>-13.52182</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.97758</t>
+          <t>-71.94899</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>595</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>146743</t>
+          <t>836972</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EL CARMELO</t>
+          <t>GAL SCHOOL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-13.51544</t>
+          <t>-13.52637</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.97453</t>
+          <t>-71.90222</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>358</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>146776</t>
+          <t>146390</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SALESIANO</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.51334</t>
+          <t>-13.52007</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.98098</t>
+          <t>-71.96246</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>619</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>146781</t>
+          <t>147158</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>BERNABE COBO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-13.51825</t>
+          <t>-13.51953</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.9833</t>
+          <t>-71.98321</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>483</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,42 +2857,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>146804</t>
+          <t>145970</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LAS MERCEDES</t>
+          <t>419 COLIBRI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.52034</t>
+          <t>-13.52134</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.97633</t>
+          <t>-71.98845</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>146818</t>
+          <t>146719</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>JOSE PARDO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-13.52171</t>
+          <t>-13.52472</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.97455</t>
+          <t>-71.97429</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>502</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>146823</t>
+          <t>146347</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-13.52103</t>
+          <t>-13.52157</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.97472</t>
+          <t>-71.97846</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>695</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>146875</t>
+          <t>146366</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JUAN LANDAZURI RICKETTS</t>
+          <t>51009 FRANCISCO SIVIRICHI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-13.52612</t>
+          <t>-13.51732</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.94926</t>
+          <t>-71.98267</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>707</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>146941</t>
+          <t>146314</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AVANTI PERU</t>
+          <t>51002 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-13.5201</t>
+          <t>-13.51734</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.98465</t>
+          <t>-71.98372</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>594</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>147158</t>
+          <t>146564</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BERNABE COBO</t>
+          <t>SAN ANTONIO ABAD</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-13.51953</t>
+          <t>-13.5258</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.98321</t>
+          <t>-71.95018</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>569</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>147356</t>
+          <t>146738</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PROYECTO INGENIERIA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-13.52502</t>
+          <t>-13.5145</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.97496</t>
+          <t>-71.97758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>147988</t>
+          <t>146743</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>50014 VIRGEN DEL CARMEN</t>
+          <t>EL CARMELO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.541976</t>
+          <t>-13.51544</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.948846</t>
+          <t>-71.97453</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>148092</t>
+          <t>146205</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>50949 EL CARMELO DE MARIA</t>
+          <t>50022 JORGE CHAVEZ CHAPARRO / JORGE CHAVEZ CHAPARRO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-13.507337</t>
+          <t>-13.52214</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.933803</t>
+          <t>-71.95226</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>704</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>148563</t>
+          <t>146818</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-13.52747</t>
+          <t>-13.52171</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.99165</t>
+          <t>-71.97455</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>577</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>148836</t>
+          <t>599923</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>SAN GABRIEL DE LOS CIELOS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-13.56926</t>
+          <t>-13.50694</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.82726</t>
+          <t>-71.99924</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,42 +3539,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>148841</t>
+          <t>717318</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI</t>
+          <t>SOR ANA DE LOS ANGELES MONTEAGUDO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-13.56911</t>
+          <t>-13.52493</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.82768</t>
+          <t>-71.9757</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>149379</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA VIRGEN DEL CARMEN</t>
+          <t>51004 SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-13.526182</t>
+          <t>-13.51869</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.945517</t>
+          <t>-71.98487</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>774</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>493097</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LIDERES</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-13.525718</t>
+          <t>-13.52103</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.945415</t>
+          <t>-71.97472</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>631</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>599923</t>
+          <t>146007</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SAN GABRIEL DE LOS CIELOS</t>
+          <t>50707 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-13.50694</t>
+          <t>-13.51909</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.99924</t>
+          <t>-71.99192</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>859</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>680598</t>
+          <t>146597</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>LA MERCED</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-13.50338</t>
+          <t>-13.51851</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-72.0234</t>
+          <t>-71.97872</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>938</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>717318</t>
+          <t>146432</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SOR ANA DE LOS ANGELES MONTEAGUDO</t>
+          <t>COMERCIO 41</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-13.52493</t>
+          <t>-13.52018</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.9757</t>
+          <t>-71.96443</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>811</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>824361</t>
+          <t>146776</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JOSE ANDRES RAZURI ESTEVEZ</t>
+          <t>SALESIANO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-13.52182</t>
+          <t>-13.51334</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.94899</t>
+          <t>-71.98098</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>918</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>836972</t>
+          <t>146130</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GAL SCHOOL</t>
+          <t>50002 LUIS VALLEJOS SANTONI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-13.52637</t>
+          <t>-13.52344</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.90222</t>
+          <t>-71.99103</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>863673</t>
+          <t>146328</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BILINGÜE MANUEL PARDO Y LAVALLE</t>
+          <t>51003 ROSARIO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-13.52745</t>
+          <t>-13.52335</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.94383</t>
+          <t>-71.9773</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>906856</t>
+          <t>146781</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SAMI RURUCHA</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-13.548</t>
+          <t>-13.51825</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.8804</t>
+          <t>-71.9833</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4131,6 +4131,192 @@
         </is>
       </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>080101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>146385</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>51015 SAN FRANCISCO DE BORJA</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-13.51544</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-71.9786</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>080101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>146286</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>50900 EDUCANDAS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-13.51689</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-71.9821</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>080101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>146154</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>HUMBERTO LUNA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-13.52399</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-71.97655</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>145913</t>
+          <t>906856</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>439 NIÑOS DE AMERICA</t>
+          <t>SAMI RURUCHA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-13.51873</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-71.96018</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-13.548</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-71.8804</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>146106</t>
+          <t>863673</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>204 MARIA MONTESSORI</t>
+          <t>BILINGÜE MANUEL PARDO Y LAVALLE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-13.52478</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-71.94585</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>-13.52745</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-71.94383</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -635,22 +635,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-13.52224</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-71.94719</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>146050</t>
+          <t>836972</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>GAL SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-13.51749</t>
+          <t>358</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-71.98641</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-13.52637</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.90222</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>146234</t>
+          <t>824361</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>50028</t>
+          <t>JOSE ANDRES RAZURI ESTEVEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-13.51909</t>
+          <t>595</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-71.95982</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>-13.52182</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-71.94899</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>146446</t>
+          <t>717318</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FORTUNATO L HERRERA</t>
+          <t>SOR ANA DE LOS ANGELES MONTEAGUDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.51971</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-71.97136</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>-13.52493</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-71.9757</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>146229</t>
+          <t>680598</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>984</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-13.51314</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-71.97915</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>-13.50338</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-72.0234</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>599923</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
+          <t>SAN GABRIEL DE LOS CIELOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-13.51907</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-71.98193</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2399</t>
+          <t>-13.50694</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>-71.99924</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>146074</t>
+          <t>493097</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>LIDERES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-13.51986</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-71.9641</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>-13.525718</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.945415</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>146267</t>
+          <t>149379</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EL NIÑO DIVINO</t>
+          <t>NUESTRA SEÑORA VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.505664</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-71.99961</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-13.526182</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.945517</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>493097</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LIDERES</t>
+          <t>ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.525718</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-71.945415</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-13.56911</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-71.82768</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>146578</t>
+          <t>148836</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE GRACIA</t>
+          <t>50036</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-13.51556</t>
+          <t>374</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-71.95138</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-13.56926</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-71.82726</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>146192</t>
+          <t>148563</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CLORINDA MATTO DE TURNER</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-13.51993</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-71.96984</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>-13.52747</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>-71.99165</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>146187</t>
+          <t>148092</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>INCA GARCILASO DE LA VEGA</t>
+          <t>50949 EL CARMELO DE MARIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-13.52069</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-71.96648</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>-13.507337</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>-71.933803</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>146253</t>
+          <t>147988</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>50048 LOS INCAS</t>
+          <t>50014 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-13.51907</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-71.9527</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-13.541976</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.948846</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>146371</t>
+          <t>147356</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
+          <t>PROYECTO INGENIERIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-13.51552</t>
+          <t>171</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-71.98855</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-13.52502</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-71.97496</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>146700</t>
+          <t>147158</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS</t>
+          <t>BERNABE COBO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-13.51719</t>
+          <t>483</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-71.98146</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-13.51953</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.98321</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>147356</t>
+          <t>146941</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PROYECTO INGENIERIA</t>
+          <t>AVANTI PERU</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-13.52502</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-71.97496</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>-13.5201</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.98465</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>148836</t>
+          <t>146875</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>50036</t>
+          <t>JUAN LANDAZURI RICKETTS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-13.56926</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-71.82726</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>-13.52612</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.94926</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>863673</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BILINGÜE MANUEL PARDO Y LAVALLE</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-13.52745</t>
+          <t>631</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-71.94383</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-13.52103</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-71.97472</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>147988</t>
+          <t>146818</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50014 VIRGEN DEL CARMEN</t>
+          <t>SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.541976</t>
+          <t>577</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-71.948846</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-13.52171</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-71.97455</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>LAS MERCEDES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-13.51926</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-71.97343</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-13.52034</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.97633</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>146272</t>
+          <t>146781</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>50828 ASHID KUMAR BAHAL</t>
+          <t>SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-13.51896</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-71.98664</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>-13.51825</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-71.9833</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,42 +1927,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>680598</t>
+          <t>146776</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>SALESIANO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-13.50338</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-72.0234</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-13.51334</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-71.98098</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>906856</t>
+          <t>146743</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SAMI RURUCHA</t>
+          <t>EL CARMELO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-13.548</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-71.8804</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-13.51544</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-71.97453</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>148092</t>
+          <t>146738</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>50949 EL CARMELO DE MARIA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-13.507337</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-71.933803</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-13.5145</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.97758</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>148563</t>
+          <t>146719</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>JOSE PARDO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-13.52747</t>
+          <t>502</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-71.99165</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-13.52472</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.97429</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>148841</t>
+          <t>146700</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANTONIO RAYMONDI</t>
+          <t>SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-13.56911</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-71.82768</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-13.51719</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-71.98146</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>146941</t>
+          <t>146597</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AVANTI PERU</t>
+          <t>LA MERCED</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-13.5201</t>
+          <t>938</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-71.98465</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-13.51851</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.97872</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>149379</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA VIRGEN DEL CARMEN</t>
+          <t>NUESTRA SEÑORA DE GRACIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-13.526182</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-71.945517</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-13.51556</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-71.95138</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>146031</t>
+          <t>146564</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>50003 SANTA ROSA</t>
+          <t>SAN ANTONIO ABAD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-13.52107</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-71.97748</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-13.5258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-71.95018</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>146210</t>
+          <t>146446</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>50023 REPUBLICA DE MEXICO</t>
+          <t>FORTUNATO L HERRERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-13.51796</t>
+          <t>544</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-71.96534</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>-13.51971</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.97136</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>146875</t>
+          <t>146432</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>JUAN LANDAZURI RICKETTS</t>
+          <t>COMERCIO 41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-13.52612</t>
+          <t>811</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-71.94926</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-13.52018</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-71.96443</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>146804</t>
+          <t>146390</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LAS MERCEDES</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-13.52034</t>
+          <t>619</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-71.97633</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-13.52007</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-71.96246</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>824361</t>
+          <t>146385</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JOSE ANDRES RAZURI ESTEVEZ</t>
+          <t>51015 SAN FRANCISCO DE BORJA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-13.52182</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-71.94899</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>-13.51544</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.9786</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>836972</t>
+          <t>146371</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GAL SCHOOL</t>
+          <t>51012 JULIO ALBERTO PONCE ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-13.52637</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-71.90222</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>-13.51552</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-71.98855</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>146390</t>
+          <t>146366</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>51009 FRANCISCO SIVIRICHI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-13.52007</t>
+          <t>707</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-71.96246</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>-13.51732</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.98267</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>147158</t>
+          <t>146352</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BERNABE COBO</t>
+          <t>GLORIOSO COLEGIO NACIONAL DE CIENCIAS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-13.51953</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-71.98321</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>-13.51907</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-71.98193</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>146347</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>419 COLIBRI</t>
+          <t>VALENTIN PANIAGUA CORAZAO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-13.52134</t>
+          <t>695</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-71.98845</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-13.52157</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-71.97846</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>146719</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>JOSE PARDO</t>
+          <t>51004 SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-13.52472</t>
+          <t>774</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-71.97429</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>-13.51869</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-71.98487</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>146347</t>
+          <t>146328</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VALENTIN PANIAGUA CORAZAO</t>
+          <t>51003 ROSARIO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-13.52157</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-71.97846</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>-13.52335</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-71.9773</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>146366</t>
+          <t>146314</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>51009 FRANCISCO SIVIRICHI</t>
+          <t>51002 ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-13.51732</t>
+          <t>594</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-71.98267</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>-13.51734</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-71.98372</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>146314</t>
+          <t>146286</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>51002 ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>50900 EDUCANDAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-13.51734</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-71.98372</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>-13.51689</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-71.9821</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>146564</t>
+          <t>146272</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SAN ANTONIO ABAD</t>
+          <t>50828 ASHID KUMAR BAHAL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-13.5258</t>
+          <t>412</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-71.95018</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>-13.51896</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-71.98664</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,42 +3229,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>146738</t>
+          <t>146267</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>EL NIÑO DIVINO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-13.5145</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-71.97758</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-13.505664</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-71.99961</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>146743</t>
+          <t>146253</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EL CARMELO</t>
+          <t>50048 LOS INCAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-13.51544</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-71.97453</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-13.51907</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-71.9527</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>146205</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>50022 JORGE CHAVEZ CHAPARRO / JORGE CHAVEZ CHAPARRO</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-13.52214</t>
+          <t>216</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-71.95226</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>-13.51909</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-71.95982</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>146818</t>
+          <t>146229</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE LIMA</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-13.52171</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-71.97455</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>-13.51314</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-71.97915</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>599923</t>
+          <t>146210</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SAN GABRIEL DE LOS CIELOS</t>
+          <t>50023 REPUBLICA DE MEXICO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-13.50694</t>
+          <t>531</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-71.99924</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-13.51796</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-71.96534</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>717318</t>
+          <t>146205</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SOR ANA DE LOS ANGELES MONTEAGUDO</t>
+          <t>50022 JORGE CHAVEZ CHAPARRO / JORGE CHAVEZ CHAPARRO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-13.52493</t>
+          <t>704</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-71.9757</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-13.52214</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-71.95226</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>146192</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>51004 SAN VICENTE DE PAUL</t>
+          <t>CLORINDA MATTO DE TURNER</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-13.51869</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-71.98487</t>
+          <t>131</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>-13.51993</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-71.96984</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>146823</t>
+          <t>146187</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-13.52103</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-71.97472</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>-13.52069</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-71.96648</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>146154</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>50707 SIMON BOLIVAR</t>
+          <t>HUMBERTO LUNA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-13.51909</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-71.99192</t>
+          <t>91</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>-13.52399</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-71.97655</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>146597</t>
+          <t>146130</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LA MERCED</t>
+          <t>50002 LUIS VALLEJOS SANTONI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-13.51851</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-71.97872</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>-13.52344</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-71.99103</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>146432</t>
+          <t>146106</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>COMERCIO 41</t>
+          <t>204 MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-13.52018</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-71.96443</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>-13.52478</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-71.94585</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>146776</t>
+          <t>146074</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SALESIANO</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-13.51334</t>
+          <t>249</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-71.98098</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>-13.51986</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-71.9641</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>146130</t>
+          <t>146069</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>50002 LUIS VALLEJOS SANTONI</t>
+          <t>88</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-13.52344</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-71.99103</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>-13.51926</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-71.97343</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>146328</t>
+          <t>146050</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>51003 ROSARIO</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-13.52335</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-71.9773</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>-13.51749</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-71.98641</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>146781</t>
+          <t>146031</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS</t>
+          <t>50003 SANTA ROSA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-13.51825</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-71.9833</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>-13.52107</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-71.97748</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>146385</t>
+          <t>146007</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>51015 SAN FRANCISCO DE BORJA</t>
+          <t>50707 SIMON BOLIVAR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-13.51544</t>
+          <t>859</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-71.9786</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>-13.51909</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-71.99192</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>146286</t>
+          <t>145970</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50900 EDUCANDAS</t>
+          <t>419 COLIBRI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-13.51689</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-71.9821</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>-13.52134</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>-71.98845</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>146154</t>
+          <t>145913</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>HUMBERTO LUNA</t>
+          <t>439 NIÑOS DE AMERICA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-13.52399</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-71.97655</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>-13.51873</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-71.96018</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">

--- a/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
+++ b/ZonasEscolares/excels/CUSCO-CUSCO-CUSCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
